--- a/daily_matches/job_matches_2026-07-14.xlsx
+++ b/daily_matches/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, OpenCV</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Snowflake, Redshift, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597ab0eb363227ed</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Software Engineer III-Generative AI Platform Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Entertainment Partners</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, MLflow, FastAPI, Kubernetes, CI/CD, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e42eebf957e43408</t>
+          <t>https://www.indeed.com/viewjob?jk=898c290cba663958</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (React + REST APIs + Dashboard Development).</t>
+          <t>Software Engineer III â€“ Generative AI Platform Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Middletown, NJ, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, Docker, Snowflake, Databricks, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, MLflow, FastAPI, Kubernetes, CI/CD, Git, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,147 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2a3e85fe811726</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3cc9f58fae8c25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Senior Data Scientist – Prognostic and Health Monitoring (HUMS)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Winfo Solutions</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, MLflow, CI/CD, Git, Snowflake, Databricks, PySpark, Tableau, Power BI, Python</t>
+          <t>Data Scientist, RAG, Prompt Engineering, CI/CD, Git, Databricks, PySpark, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1691b4d7b52de9</t>
+          <t>https://www.indeed.com/viewjob?jk=d9967c1f7bc9239f</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Network Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Berkley</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a73241a9f911fad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Jenkins, Git, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d61e2342460c201b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java Script) - Hybrid (Entry/Mid Level)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bloomington, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efa79bd34e7b08b4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-14.xlsx
+++ b/daily_matches/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,227 +486,262 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Snowflake, Redshift, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, LightGBM, MLflow, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=999430307d17348b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III-Generative AI Platform Engineering</t>
+          <t>AI Data Scientist – Enterprise AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, MLflow, FastAPI, Kubernetes, CI/CD, Git, Kafka</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898c290cba663958</t>
+          <t>https://www.indeed.com/viewjob?jk=99adad3741fea3e4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III â€“ Generative AI Platform Engineering</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, MLflow, FastAPI, Kubernetes, CI/CD, Git, Kafka</t>
+          <t>Generative AI, RAG, Gemini, GitHub Actions, Git, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3cc9f58fae8c25</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Prognostic and Health Monitoring (HUMS)</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Cruz, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, CI/CD, Git, Databricks, PySpark, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, GitHub Actions, Git, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9967c1f7bc9239f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Network Automation Engineer</t>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73241a9f911fad1</t>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Mobile Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Jenkins, Git, PySpark, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e2342460c201b</t>
+          <t>https://www.indeed.com/viewjob?jk=10c046cabe3a2b8b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer (Java Script) - Hybrid (Entry/Mid Level)</t>
+          <t>Mobile Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=611a5ab812fa419a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Power Factors</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efa79bd34e7b08b4</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fabf7ca4210ce0f7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-14.xlsx
+++ b/daily_matches/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, LightGBM, MLflow, Snowflake, Databricks, Python</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999430307d17348b</t>
+          <t>https://www.indeed.com/viewjob?jk=9694fb70191ff26e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Data Scientist – Enterprise AI</t>
+          <t>Forward Deployed Engineer - Software Development Engineer – Artificial Intelligence (AI) - #4883</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>GRAIL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, Databricks, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99adad3741fea3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e882afc13462e6d2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Gen AI Full stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BN Associates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, GitHub Actions, Git, Kafka, Hadoop, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Synapse, Docker, Jenkins, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2e14879c963489</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, GitHub Actions, Git, Kafka, Hadoop, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, BigQuery, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,147 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mobile Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Berwyn, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10c046cabe3a2b8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mobile Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Berwyn, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=611a5ab812fa419a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Power Factors</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fabf7ca4210ce0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=285df15218e5f195</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-14.xlsx
+++ b/daily_matches/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9694fb70191ff26e</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Software Development Engineer – Artificial Intelligence (AI) - #4883</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GRAIL</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e882afc13462e6d2</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gen AI Full stack Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BN Associates</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Synapse, Docker, Jenkins, Databricks, Python, R, Java</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,1092 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2e14879c963489</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Backend AI)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>iHerb</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Redshift, BigQuery, Data Lake, MLflow, Docker, CI/CD, Databricks, BigQuery</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67dc4ab0c6df1a50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Native Developer- Europe</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Native Builder-Europe</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b441ee40467ecee</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Full Stack Developer III - Private Markets Applications</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Neuberger Berman</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer II | ML &amp; AI (REMOTE)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51aa93a97bd82791</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a47c5e7dbbd108ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dot Net/GCP - Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49326ea3014f6d18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, CI/CD, Git, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Escalent</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure and DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hillsboro, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b750350269023244</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e9fc4c8cab0eba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Royal Oak, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07d7778d2e6d2856</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8b994988a2e5b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dee6a1bae9970ca0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Typescript</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d5ed7427cab7ec2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Verisure</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Uniontown, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Solutions Engineer - Data Visualization</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>11.1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, BigQuery, BigQuery, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=285df15218e5f195</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, Dataflow, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Arbitration Forums Inc.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c27f2a9eec45412</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Asurion</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Kafka, MongoDB, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40c9dbfc828a2c5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Techtorch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02c99ca30965abe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer II - AI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>iHerb</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1677ba023ceaf09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Technical Solutioning Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AIG</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b70e57b73a5c1357</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Technical Solutioning Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AIG</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00d8441eb1a9e6d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20bc413e7142e2cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Engineer, Senior Systems</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Austin Community College</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8ccefb7068012d5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-14.xlsx
+++ b/daily_matches/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>MHK TECH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb8eceec6d1de0a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Cloud Transformation Senior Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=57362c44cdaea54f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Junior Architect / Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, FastAPI, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3619060bd1d7f4c4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iHerb</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Redshift, BigQuery, Data Lake, MLflow, Docker, CI/CD, Databricks, BigQuery</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67dc4ab0c6df1a50</t>
+          <t>https://www.indeed.com/viewjob?jk=17538ed65a380373</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Native Developer- Europe</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b441ee40467ecee</t>
+          <t>https://www.indeed.com/viewjob?jk=cab0c6a9b9ce8cd5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Dot Net/GCP - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=36c2377b03f53097</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II | ML &amp; AI (REMOTE)</t>
+          <t>Senior Data Engineer, RiverX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Data Lake, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51aa93a97bd82791</t>
+          <t>https://www.indeed.com/viewjob?jk=23e4c4558e00ed62</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Tanium Platform Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a47c5e7dbbd108ad</t>
+          <t>https://www.indeed.com/viewjob?jk=de84cd851beb1d97</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dot Net/GCP - Senior Software Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>McCarthy Holdings</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49326ea3014f6d18</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd3fa926f7854be</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Levittown, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, CI/CD, Git, Databricks, Kafka, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=ae46f57dc6060fd3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>Beth Israel Lahey Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, Kubernetes, AKS, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=6069963e7fe2e357</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Infrastructure and DevOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b750350269023244</t>
+          <t>https://www.indeed.com/viewjob?jk=4bda76b15a2f8e76</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>AI Arhitect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e9fc4c8cab0eba5</t>
+          <t>https://www.indeed.com/viewjob?jk=5600b249edcd6cf1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Chickasaw Nation Industries</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d7778d2e6d2856</t>
+          <t>https://www.indeed.com/viewjob?jk=a7531be7a30e5cd8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Sr AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8b994988a2e5b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda396b569e01bb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Senior GTM Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>PandaDoc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee6a1bae9970ca0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a4a0a8c4489d807</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Typescript</t>
+          <t>Senior GTM Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>PandaDoc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5ed7427cab7ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=45ff7bb63f6baa68</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior GTM Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>PandaDoc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8323cc7e4f71834</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Senior GTM Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>PandaDoc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Dataflow, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,322 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Arbitration Forums Inc.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c27f2a9eec45412</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Kafka, MongoDB, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40c9dbfc828a2c5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Techtorch</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Gemini, FastAPI, Docker, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02c99ca30965abe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer II - AI</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>iHerb</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1677ba023ceaf09</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Technical Solutioning Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>AIG</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b70e57b73a5c1357</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Technical Solutioning Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>AIG</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00d8441eb1a9e6d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Thomson Reuters</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Eagan, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20bc413e7142e2cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CT, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, PySpark, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Engineer, Senior Systems</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ccefb7068012d5</t>
+          <t>https://www.indeed.com/viewjob?jk=591d718e5f5c4687</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-14.xlsx
+++ b/daily_matches/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MHK TECH</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Athena, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb8eceec6d1de0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0663114dfd06c9eb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
+          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
+          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Transformation Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57362c44cdaea54f</t>
+          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior Architect / Senior Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>24.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Snowflake, Databricks, PySpark, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Data AI Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9de5ac8d42dd8ec2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, FastAPI, CI/CD, Terraform, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3619060bd1d7f4c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4fedd008cd06663f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Abel, AL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, S3, EC2, BigQuery, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17538ed65a380373</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6cef820b87ba89</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Senior Software Engineer - Machine Learning (Remote)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Dataflow, Git, BigQuery, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=0ef4f0fa082366da</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analyst, AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, BigQuery, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab0c6a9b9ce8cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=da7a7fc69312366b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dot Net/GCP - Senior Software Engineer</t>
+          <t>Data Scientist, Upstream Development</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36c2377b03f53097</t>
+          <t>https://www.indeed.com/viewjob?jk=0d46734ec9f6d145</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, RiverX</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Data Lake, Git, Snowflake, Python, SQL</t>
+          <t>RAG, Cortex, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23e4c4558e00ed62</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tanium Platform Security Engineer</t>
+          <t>Data Science Intern (AI &amp; Machine Learning)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Sikka Software</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, Hadoop, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de84cd851beb1d97</t>
+          <t>https://www.indeed.com/viewjob?jk=de6695d0d8442c4c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>McCarthy Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Python, SQL</t>
+          <t>RAG, Redshift, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Redshift, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd3fa926f7854be</t>
+          <t>https://www.indeed.com/viewjob?jk=ff8b1cf198867c72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google Cloud Platform (GCP) Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Levittown, NY, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae46f57dc6060fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3f70853d15c71a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Beth Israel Lahey Health</t>
+          <t>ClearlyRated</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Kubernetes, AKS, NoSQL, Python, SQL, R, Java</t>
+          <t>BigQuery, Dataflow, Kubernetes, CI/CD, BigQuery, Kafka, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6069963e7fe2e357</t>
+          <t>https://www.indeed.com/viewjob?jk=a95ccb45ebe7a6af</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bda76b15a2f8e76</t>
+          <t>https://www.indeed.com/viewjob?jk=d95f616f8a93e76b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Arhitect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, BigQuery, Terraform, BigQuery, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5600b249edcd6cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=9009c2eb9f3c4426</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chickasaw Nation Industries</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, BigQuery, Terraform, BigQuery, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7531be7a30e5cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ebe5404d26e6f4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr AI Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda396b569e01bb</t>
+          <t>https://www.indeed.com/viewjob?jk=234c4dd3d071f3aa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior GTM Data Scientist</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
+          <t>LangChain, RAG, LLaMA, S3, Redshift, BigQuery, Docker, Git, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a4a0a8c4489d807</t>
+          <t>https://www.indeed.com/viewjob?jk=462dfe5f73f04e29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior GTM Data Scientist</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
+          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,77 +1266,567 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ff7bb63f6baa68</t>
+          <t>https://www.indeed.com/viewjob?jk=dd34e7f31155f48b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior GTM Data Scientist</t>
+          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8323cc7e4f71834</t>
+          <t>https://www.indeed.com/viewjob?jk=e953e5a091cd9103</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior GTM Data Scientist</t>
+          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5eed877691f0ccfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior QA Automation Engineer with Capital Markets and Gen AI experience</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aab9cf75379203e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior SDET with FinTech &amp; Capital Markets experience</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83c1279a95bd40d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Quality Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10e7ce14a613c9a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>UX Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Client Resources, Inc.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=591d718e5f5c4687</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kubernetes, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70f78135788fbafd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Power Factors</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1bbe8e3704dd018</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Affinity</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb2ec4b5b64be8b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Affinity</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1165c13f7f9d46b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Affinity</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d82d3c6fafd90754</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer, C++/Robotics</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Path Robotics, Inc.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, C++</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c74cc572e558bab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Cyber Security Engineer - Automation, Data Center &amp; Networking Security</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Latitude AI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a08e83a46ad2e463</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Azure Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=315998e7f22215dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer - E-commerce</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b298a63faaa1b342</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-14.xlsx
+++ b/daily_matches/job_matches_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>AI Engineer - Automated Channels Transformation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Fifth Third Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, Athena, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0663114dfd06c9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc5ddbaa8a2f4e7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI &amp; Financial Engineering Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
+          <t>https://www.indeed.com/viewjob?jk=241a34851225e025</t>
         </is>
       </c>
     </row>
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
+          <t>https://www.indeed.com/viewjob?jk=020e432808447458</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
+          <t>https://www.indeed.com/viewjob?jk=2735fe2f7042b983</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data AI Architect</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de5ac8d42dd8ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior AI Engineer, Enterprise</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Cortex, FastAPI, Docker, Kubernetes, CI/CD, Snowflake, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fedd008cd06663f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8354fb754f8847f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abel, AL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, S3, EC2, BigQuery, Docker, Kubernetes</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6cef820b87ba89</t>
+          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=52c472962c791de2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning (Remote)</t>
+          <t>Data Scientist, Analytics and Modelling</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, BigQuery, Dataflow, Git, BigQuery, Python</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Git, Redshift, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ef4f0fa082366da</t>
+          <t>https://www.indeed.com/viewjob?jk=9439d62d21cdb7b2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analyst, AI Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, BigQuery, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7a7fc69312366b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d19d5af711dae1a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist, Upstream Development</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Git, BigQuery, Kafka, Tableau, Power BI, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d46734ec9f6d145</t>
+          <t>https://www.indeed.com/viewjob?jk=14af21d8d4a25c44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>Technology Risk Specialist | Technology Risk Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c1d78f9208f69e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Science Intern (AI &amp; Machine Learning)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sikka Software</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>RAG, CI/CD, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6695d0d8442c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>AI Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nextiva</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Redshift, Python</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff8b1cf198867c72</t>
+          <t>https://www.indeed.com/viewjob?jk=83c2f2aeebb5b8d3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Google Cloud Platform (GCP) Engineer</t>
+          <t>Senior Full-Stack &amp; Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>Gumball Digital</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3f70853d15c71a</t>
+          <t>https://www.indeed.com/viewjob?jk=686567493b59323b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>AI Innovation Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ClearlyRated</t>
+          <t>Holland America Line</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Kubernetes, CI/CD, BigQuery, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>LangChain, RAG, Pinecone, ChromaDB, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95ccb45ebe7a6af</t>
+          <t>https://www.indeed.com/viewjob?jk=0c9a029730959ed4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95f616f8a93e76b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7911453e562688</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Terraform, BigQuery, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, Hadoop, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9009c2eb9f3c4426</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Agentic AI Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WellSky</t>
+          <t>Strata Decision Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Terraform, BigQuery, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, CI/CD, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ebe5404d26e6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a4b99cce0d656e7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Prompt Engineering, MySQL, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234c4dd3d071f3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fc8fefdd38167c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>A.I. Solutions Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Waste Connections</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, S3, Redshift, BigQuery, Docker, Git, BigQuery, Redshift</t>
+          <t>Data Scientist, Data Lake, CI/CD, Terraform, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462dfe5f73f04e29</t>
+          <t>https://www.indeed.com/viewjob?jk=32d131b39d181210</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer Intern (1st Shift)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, Apache Airflow, CI/CD, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd34e7f31155f48b</t>
+          <t>https://www.indeed.com/viewjob?jk=638da22ca8feb1db</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Docker, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e953e5a091cd9103</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer IV — CI/CD Pipeline &amp; Platform Engineering</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed877691f0ccfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e0b7b622ddb355</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer with Capital Markets and Gen AI experience</t>
+          <t>Pricing Data Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Databricks, Tableau, Quicksight, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,462 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aab9cf75379203e</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior SDET with FinTech &amp; Capital Markets experience</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83c1279a95bd40d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Quality Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10e7ce14a613c9a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>UX Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Client Resources, Inc.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, Kubernetes, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70f78135788fbafd</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Power Factors</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1bbe8e3704dd018</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Affinity</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2ec4b5b64be8b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Affinity</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1165c13f7f9d46b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Affinity</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d82d3c6fafd90754</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Software Engineer, C++/Robotics</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Path Robotics, Inc.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, C++</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c74cc572e558bab8</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Cyber Security Engineer - Automation, Data Center &amp; Networking Security</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Latitude AI</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a08e83a46ad2e463</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Azure Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=315998e7f22215dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer - E-commerce</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b298a63faaa1b342</t>
+          <t>https://www.indeed.com/viewjob?jk=b58c89cd16f9c71b</t>
         </is>
       </c>
     </row>
